--- a/isms-core-framework/A.7-physical-controls/isms-a.7.10-storage-media/WKBK/90_workbooks/ISMS-IMP-A.7.10.1_Storage_Media_Inventory_20260208.xlsx
+++ b/isms-core-framework/A.7-physical-controls/isms-a.7.10-storage-media/WKBK/90_workbooks/ISMS-IMP-A.7.10.1_Storage_Media_Inventory_20260208.xlsx
@@ -859,7 +859,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>- PCI DSS v4.0 Requirement 9.4: Media protection</t>
+          <t>- PCI DSS v4.0.1 Requirement 9.4: Media protection</t>
         </is>
       </c>
     </row>
